--- a/products to monitor.xlsx
+++ b/products to monitor.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -467,7 +467,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Сыр Ламбер 50% БЗМЖ 500г</t>
+          <t>Сыр Ламбер</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Бананы Global Village</t>
+          <t>Бананы</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -527,7 +527,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Масло Global Village оливковое</t>
+          <t>Масло</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,7 +547,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Филе бедра индейки Индилайт</t>
+          <t>Филе бедра индейки</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Творог пластовой 4-6% Из Лавки</t>
+          <t>Творог пластовой</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Масло сладкосливочное Экомилк</t>
+          <t>Масло сладкосливочное</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Филе грудки индейки Индилайт</t>
+          <t>Филе грудки индейки</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -647,12 +647,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Филе бедра индейки ИндиЛайт охлажденное, 410г</t>
+          <t>Яйцо Окское столовое С2 10шт.</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Яйца</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,18 +661,18 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>1660.83</v>
+        <v>1652.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Яйцо Окское столовое С2 10шт.</t>
+          <t>Стейк</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Яйца</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -681,18 +681,18 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>1652.04</v>
+        <v>1624.89</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Стейк из грудки индейки ИндиЛайт охлажденный,</t>
+          <t>Киви</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -701,18 +701,18 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1624.89</v>
+        <v>1601.5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Стейк из грудки индейки ИндиЛайт</t>
+          <t>Напиток Станция Молочная Снежок</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -721,18 +721,18 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>1623.84</v>
+        <v>1587.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Киви спелое 700г</t>
+          <t>Молоко Алексеевское сгущенное цельное с</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -741,18 +741,18 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>1601.5</v>
+        <v>1459.47</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Напиток Станция Молочная Снежок</t>
+          <t>Салат Айсберг 1шт.</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -761,18 +761,18 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>1587.79</v>
+        <v>1450.61</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Молоко Алексеевское сгущенное цельное с</t>
+          <t>MONARCH Кофе</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -781,18 +781,18 @@
         </is>
       </c>
       <c r="D17" s="3" t="n">
-        <v>1459.47</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Салат Айсберг 1шт.</t>
+          <t>Печенье Belvita Утреннее</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -801,18 +801,18 @@
         </is>
       </c>
       <c r="D18" s="3" t="n">
-        <v>1450.61</v>
+        <v>1264.43</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>MONARCH Кофе ORIG.жар.зер.800г</t>
+          <t>Кукуруза консервированная Бондюэль сладкая</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -821,18 +821,18 @@
         </is>
       </c>
       <c r="D19" s="3" t="n">
-        <v>1349</v>
+        <v>1240.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Печенье Belvita Утреннее со злаковыми хлопьями</t>
+          <t>Кофе в зернах Monarch Ориджинал</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -841,18 +841,18 @@
         </is>
       </c>
       <c r="D20" s="3" t="n">
-        <v>1264.43</v>
+        <v>1202.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Кукуруза консервированная Бондюэль сладкая</t>
+          <t>Пельмени Сибирская Коллекция мини с</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -861,18 +861,18 @@
         </is>
       </c>
       <c r="D21" s="3" t="n">
-        <v>1240.52</v>
+        <v>1194.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Кофе в зернах Monarch Ориджинал натуральный</t>
+          <t>Рукола</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -881,18 +881,18 @@
         </is>
       </c>
       <c r="D22" s="3" t="n">
-        <v>1202.01</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Пельмени Сибирская Коллекция мини с</t>
+          <t>Печенье детское Honey Kid Обогащенное</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -901,58 +901,58 @@
         </is>
       </c>
       <c r="D23" s="3" t="n">
-        <v>1194.03</v>
+        <v>1001.01</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Рукола</t>
+          <t>Сосиски Клинский Молочные ГОСТ 470г</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Высокий</t>
+          <t>Средний</t>
         </is>
       </c>
       <c r="D24" s="3" t="n">
-        <v>1017</v>
+        <v>987.52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Печенье детское Honey Kid Обогащенное</t>
+          <t>Молоко Простоквашино отборное</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Высокий</t>
+          <t>Средний</t>
         </is>
       </c>
       <c r="D25" s="3" t="n">
-        <v>1001.01</v>
+        <v>983.01</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Сосиски Клинский Молочные ГОСТ 470г</t>
+          <t>Биолакт Тема сладкий</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="D26" s="3" t="n">
-        <v>987.52</v>
+        <v>918.66</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Молоко Простоквашино отборное</t>
+          <t>Йогурт Простоквашино Греческий</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -981,18 +981,18 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>983.01</v>
+        <v>898.76</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Филе грудки индейки</t>
+          <t>Салат Рукола</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1001,18 +1001,18 @@
         </is>
       </c>
       <c r="D28" s="3" t="n">
-        <v>936.12</v>
+        <v>853.73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Биолакт Тема сладкий с 8 мес. 3.2% БЗМЖ 208г</t>
+          <t>Пармезан Trattoria di Maestro Turatti</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1021,18 +1021,18 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>918.66</v>
+        <v>803.23</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Йогурт Простоквашино Греческий 2% 235г</t>
+          <t>Батон Коломенское Нарезной нарезка 400г</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1041,18 +1041,18 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>898.76</v>
+        <v>797.9299999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Сыр Ламбер</t>
+          <t>Тартин злаковый</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1061,18 +1061,18 @@
         </is>
       </c>
       <c r="D31" s="3" t="n">
-        <v>887</v>
+        <v>756</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Салат Рукола Global Village, 75г</t>
+          <t>Творог Станция Молочная обезжиренный</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1081,18 +1081,18 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>853.73</v>
+        <v>677.75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Пармезан Trattoria di Maestro Turatti</t>
+          <t>Томаты черри оранжевые на ветке Сладкая ягода</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1101,13 +1101,13 @@
         </is>
       </c>
       <c r="D33" s="3" t="n">
-        <v>803.23</v>
+        <v>677</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Батон Коломенское Нарезной нарезка 400г</t>
+          <t>Батон Нарезной Коломенское</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1121,18 +1121,18 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>797.9299999999999</v>
+        <v>660.24</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Филе бедра индейки ИндиЛайт охлажденное,</t>
+          <t>Молоко отборное 3,4-4,5%</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1141,18 +1141,18 @@
         </is>
       </c>
       <c r="D35" s="3" t="n">
-        <v>782.55</v>
+        <v>657</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Тартин злаковый Из Лавки</t>
+          <t>Крылья куриные охлажденные</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1161,18 +1161,18 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>756</v>
+        <v>641.92</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Творог Станция Молочная обезжиренный</t>
+          <t>ИНДИЛ.Филе бедра инд.охл.410г</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1181,19 +1181,18 @@
         </is>
       </c>
       <c r="D37" s="3" t="n">
-        <v>677.75</v>
+        <v>612.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Томаты черри оранжевые на ветке
-Сладкая ягода</t>
+          <t>Огурец длинный</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1202,18 +1201,18 @@
         </is>
       </c>
       <c r="D38" s="3" t="n">
-        <v>677</v>
+        <v>604.33</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Батон Нарезной Коломенское</t>
+          <t>Форель слабосолёная Из Лавки кусок</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1222,14 +1221,13 @@
         </is>
       </c>
       <c r="D39" s="3" t="n">
-        <v>660.24</v>
+        <v>600</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Молоко отборное 3,4-4,5% Из
-Лавки</t>
+          <t>ЛАМБЕР Сыр твердый</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1243,18 +1241,18 @@
         </is>
       </c>
       <c r="D40" s="3" t="n">
-        <v>657</v>
+        <v>597.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Крылья куриные охлажденные</t>
+          <t>Сахар белый свекловичный кристаллический 3кг</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1263,18 +1261,18 @@
         </is>
       </c>
       <c r="D41" s="3" t="n">
-        <v>641.92</v>
+        <v>591.27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ИНДИЛ.Филе бедра инд.охл.410г</t>
+          <t>Мед Медович Луговой</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1283,18 +1281,18 @@
         </is>
       </c>
       <c r="D42" s="3" t="n">
-        <v>612.38</v>
+        <v>579.98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Огурец длинный, 1шт</t>
+          <t>Биолакт Тёма</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1303,14 +1301,13 @@
         </is>
       </c>
       <c r="D43" s="3" t="n">
-        <v>604.33</v>
+        <v>571</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Форель слабосолёная Из Лавки
-кусок</t>
+          <t>Чай Азерчай Букет черный байховый</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1324,18 +1321,18 @@
         </is>
       </c>
       <c r="D44" s="3" t="n">
-        <v>600</v>
+        <v>562.79</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>ЛАМБЕР Сыр твердый 50% фас.1кг</t>
+          <t>Картофель отечественный</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1344,18 +1341,18 @@
         </is>
       </c>
       <c r="D45" s="3" t="n">
-        <v>597.99</v>
+        <v>551.7</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Сахар белый свекловичный кристаллический 3кг</t>
+          <t>Сахар белый песок 1кг</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1364,18 +1361,18 @@
         </is>
       </c>
       <c r="D46" s="3" t="n">
-        <v>591.27</v>
+        <v>540.03</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Мед Медович Луговой натуральный 250г</t>
+          <t>Молоко кокосовое Aroy-D</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1384,13 +1381,13 @@
         </is>
       </c>
       <c r="D47" s="3" t="n">
-        <v>579.98</v>
+        <v>532</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Биолакт Тёма</t>
+          <t>Творог мягкий</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1404,93 +1401,93 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>571</v>
+        <v>518.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Чай Азерчай Букет черный байховый</t>
+          <t>Сметана Искренне Ваш</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Средний</t>
+          <t>Низкий</t>
         </is>
       </c>
       <c r="D49" s="3" t="n">
-        <v>562.79</v>
+        <v>497.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Картофель отечественный</t>
+          <t>Творог Савушкин Мягкий обезжиренный</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Средний</t>
+          <t>Низкий</t>
         </is>
       </c>
       <c r="D50" s="3" t="n">
-        <v>551.7</v>
+        <v>497.23</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Сахар белый песок 1кг</t>
+          <t>Молоко 3,2%</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Средний</t>
+          <t>Низкий</t>
         </is>
       </c>
       <c r="D51" s="3" t="n">
-        <v>540.03</v>
+        <v>464.22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Молоко кокосовое Aroy-D</t>
+          <t>Масло Золотая семечка подсолнечное</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Средний</t>
+          <t>Низкий</t>
         </is>
       </c>
       <c r="D52" s="3" t="n">
-        <v>532</v>
+        <v>443.09</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Творог мягкий 5% Простоквашино</t>
+          <t>Молоко 2,5% Простоквашино</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1500,22 +1497,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Средний</t>
+          <t>Низкий</t>
         </is>
       </c>
       <c r="D53" s="3" t="n">
-        <v>518.5</v>
+        <v>428.9</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Сметана Искренне Ваш 10% БЗМЖ 300г</t>
+          <t>Чай черный Dilmah Ceylon Orange Pekoe</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1524,18 +1521,18 @@
         </is>
       </c>
       <c r="D54" s="3" t="n">
-        <v>497.98</v>
+        <v>416.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Творог Савушкин Мягкий обезжиренный</t>
+          <t>КРУГ Кекс ВЕСЕННИЙ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1544,18 +1541,18 @@
         </is>
       </c>
       <c r="D55" s="3" t="n">
-        <v>497.23</v>
+        <v>399.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Молоко 3,2% Из Лавки</t>
+          <t>Печенье Belvita Утреннее витаминизированное</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1564,18 +1561,18 @@
         </is>
       </c>
       <c r="D56" s="3" t="n">
-        <v>464.22</v>
+        <v>392.97</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Масло Золотая семечка подсолнечное</t>
+          <t>Молоко сгущенное Алексеевское цельное с</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1584,18 +1581,18 @@
         </is>
       </c>
       <c r="D57" s="3" t="n">
-        <v>443.09</v>
+        <v>390.84</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Молоко 2,5% Простоквашино</t>
+          <t>Томаты Рост Медовые Черри оранжевые</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -1604,18 +1601,18 @@
         </is>
       </c>
       <c r="D58" s="3" t="n">
-        <v>428.9</v>
+        <v>383.37</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Чай черный Dilmah Ceylon Orange Pekoe</t>
+          <t>Вафли Коровка Топленое молоко 300г</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -1624,18 +1621,18 @@
         </is>
       </c>
       <c r="D59" s="3" t="n">
-        <v>416.5</v>
+        <v>367.52</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>КРУГ Кекс ВЕСЕННИЙ с цукат.500г</t>
+          <t>Огурцы гладкие Ботаника</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -1644,18 +1641,18 @@
         </is>
       </c>
       <c r="D60" s="3" t="n">
-        <v>399.99</v>
+        <v>358</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Печенье Belvita Утреннее витаминизированное со</t>
+          <t>Томаты</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -1664,18 +1661,18 @@
         </is>
       </c>
       <c r="D61" s="3" t="n">
-        <v>392.97</v>
+        <v>353.41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Молоко сгущенное Алексеевское цельное с</t>
+          <t>Банан</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -1684,18 +1681,18 @@
         </is>
       </c>
       <c r="D62" s="3" t="n">
-        <v>390.84</v>
+        <v>348.8</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Томаты Рост Медовые Черри оранжевые</t>
+          <t>Молоко Станция Молочная</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1704,18 +1701,18 @@
         </is>
       </c>
       <c r="D63" s="3" t="n">
-        <v>383.37</v>
+        <v>347.63</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Вафли Коровка Топленое молоко 300г</t>
+          <t>Салат Айсберг Маркет Fresh</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -1724,18 +1721,18 @@
         </is>
       </c>
       <c r="D64" s="3" t="n">
-        <v>367.52</v>
+        <v>338.98</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Огурцы гладкие Ботаника</t>
+          <t>Филе индейки Рестория малое 500г</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1744,13 +1741,13 @@
         </is>
       </c>
       <c r="D65" s="3" t="n">
-        <v>358</v>
+        <v>329.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Томаты Global village Selection Бакинские</t>
+          <t>Огурцы Корнишон</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1764,18 +1761,18 @@
         </is>
       </c>
       <c r="D66" s="3" t="n">
-        <v>353.41</v>
+        <v>321.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Банан</t>
+          <t>Салат Руккола</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1784,18 +1781,18 @@
         </is>
       </c>
       <c r="D67" s="3" t="n">
-        <v>348.8</v>
+        <v>317.35</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Молоко Станция Молочная</t>
+          <t>Крыло куриное Петелинка целое</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1804,18 +1801,18 @@
         </is>
       </c>
       <c r="D68" s="3" t="n">
-        <v>347.63</v>
+        <v>310.16</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Салат Айсберг Маркет Fresh, 1шт</t>
+          <t>Конфеты ДаЁжъ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1824,13 +1821,13 @@
         </is>
       </c>
       <c r="D69" s="3" t="n">
-        <v>338.98</v>
+        <v>304.82</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Филе индейки Рестория малое 500г</t>
+          <t>Стейк из грудки индейки</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1844,18 +1841,18 @@
         </is>
       </c>
       <c r="D70" s="3" t="n">
-        <v>329.99</v>
+        <v>304</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Огурцы Корнишон</t>
+          <t>Горошек консервированный Бондюэль нежный</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1864,18 +1861,18 @@
         </is>
       </c>
       <c r="D71" s="3" t="n">
-        <v>321.1</v>
+        <v>297.85</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Салат Руккола Global Village, 75г</t>
+          <t>Кешью Красная цена жареный 100г</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1884,18 +1881,18 @@
         </is>
       </c>
       <c r="D72" s="3" t="n">
-        <v>317.35</v>
+        <v>289.11</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Сыр Ламбер 50% БЗМЖ 230г</t>
+          <t>Индейка</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1904,18 +1901,18 @@
         </is>
       </c>
       <c r="D73" s="3" t="n">
-        <v>313.38</v>
+        <v>277.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Крыло куриное Петелинка целое охлажденное</t>
+          <t>Йогурт греческий Простоквашино</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1924,18 +1921,18 @@
         </is>
       </c>
       <c r="D74" s="3" t="n">
-        <v>310.16</v>
+        <v>274</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Конфеты ДаЁжъ с карамелью, арахисом и криспи</t>
+          <t>Чечевица</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1944,19 +1941,18 @@
         </is>
       </c>
       <c r="D75" s="3" t="n">
-        <v>304.82</v>
+        <v>272.2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Стейк из грудки индейки
-Индилайт</t>
+          <t>Яблоки Медовый хруст</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1965,18 +1961,18 @@
         </is>
       </c>
       <c r="D76" s="3" t="n">
-        <v>304</v>
+        <v>269</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Горошек консервированный Бондюэль нежный</t>
+          <t>Лимоны</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1985,18 +1981,18 @@
         </is>
       </c>
       <c r="D77" s="3" t="n">
-        <v>297.85</v>
+        <v>267.96</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Бананы</t>
+          <t>Микс салатов рукола и радиччо</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2005,18 +2001,18 @@
         </is>
       </c>
       <c r="D78" s="3" t="n">
-        <v>296.5</v>
+        <v>261</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Кешью Красная цена жареный 100г</t>
+          <t>Печенье сдобное Шарлиз Курабье</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2025,18 +2021,18 @@
         </is>
       </c>
       <c r="D79" s="3" t="n">
-        <v>289.11</v>
+        <v>260.79</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Йогурт Простоквашино Греческий 2%, 235г</t>
+          <t>Печенье Вкус &amp; Польза Овсяное 200г</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2045,18 +2041,18 @@
         </is>
       </c>
       <c r="D80" s="3" t="n">
-        <v>284.97</v>
+        <v>258.46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Индейка ИндиЛайт духовая бескостная</t>
+          <t>Творог Искренне Ваш</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2065,18 +2061,18 @@
         </is>
       </c>
       <c r="D81" s="3" t="n">
-        <v>277.99</v>
+        <v>253.74</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Йогурт греческий Простоквашино</t>
+          <t>Хлебцы Шведские Бурже Хлебный дом</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2085,18 +2081,18 @@
         </is>
       </c>
       <c r="D82" s="3" t="n">
-        <v>274</v>
+        <v>253</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Чечевица Global Village красная 450г</t>
+          <t>Чай Greenfield Золотой цейлон черный</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2105,18 +2101,18 @@
         </is>
       </c>
       <c r="D83" s="3" t="n">
-        <v>272.2</v>
+        <v>249.99</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Яблоки Медовый хруст</t>
+          <t>Кукуруза свежая</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2125,18 +2121,18 @@
         </is>
       </c>
       <c r="D84" s="3" t="n">
-        <v>269</v>
+        <v>249</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Лимоны</t>
+          <t>Творог 3,9% Агуша яблоко-банан</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2145,18 +2141,18 @@
         </is>
       </c>
       <c r="D85" s="3" t="n">
-        <v>267.96</v>
+        <v>245</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Микс салатов рукола и радиччо</t>
+          <t>Творог Агуша груша</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2165,18 +2161,18 @@
         </is>
       </c>
       <c r="D86" s="3" t="n">
-        <v>261</v>
+        <v>241.36</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Печенье сдобное Шарлиз Курабье с вишневой</t>
+          <t>Яйцо С1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Яйца</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2185,18 +2181,18 @@
         </is>
       </c>
       <c r="D87" s="3" t="n">
-        <v>260.79</v>
+        <v>239</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Печенье Вкус &amp; Польза Овсяное 200г</t>
+          <t>Творожок Простоквашино Голубика-банан</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2205,18 +2201,18 @@
         </is>
       </c>
       <c r="D88" s="3" t="n">
-        <v>258.46</v>
+        <v>232.9</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Творог Искренне Ваш 5% БЗМЖ 180г</t>
+          <t>Пакеты для мусора Liberhaus сверхпрочные с</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Упаковка/прочее</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2225,19 +2221,18 @@
         </is>
       </c>
       <c r="D89" s="3" t="n">
-        <v>253.74</v>
+        <v>232.72</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Хлебцы Шведские Бурже Хлебный
-дом</t>
+          <t>Творог Тема клубника, банан</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2246,18 +2241,18 @@
         </is>
       </c>
       <c r="D90" s="3" t="n">
-        <v>253</v>
+        <v>230.93</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Чай Greenfield Золотой цейлон черный</t>
+          <t>Томаты Рост Медовые Черри оранжевые круглые</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2266,18 +2261,18 @@
         </is>
       </c>
       <c r="D91" s="3" t="n">
-        <v>249.99</v>
+        <v>212.04</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Кукуруза свежая</t>
+          <t>ОКСКОЕ Яйцо стол.2кат.10шт</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Яйца</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2286,18 +2281,18 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>249</v>
+        <v>199.98</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Творог 3,9% Агуша яблоко-банан</t>
+          <t>Доставка H79963842837</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2306,18 +2301,18 @@
         </is>
       </c>
       <c r="D93" s="3" t="n">
-        <v>245</v>
+        <v>199</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Творог Агуша груша</t>
+          <t>Сушки Семейка Озби ванильные 200г</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2326,18 +2321,18 @@
         </is>
       </c>
       <c r="D94" s="3" t="n">
-        <v>241.36</v>
+        <v>198.93</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Яйцо С1</t>
+          <t>Кетчуп Heinz томатный 800г</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Яйца</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2346,18 +2341,18 @@
         </is>
       </c>
       <c r="D95" s="3" t="n">
-        <v>239</v>
+        <v>192.58</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Творожок Простоквашино Голубика-банан</t>
+          <t>Салат Айсберг Вкусвилл ~450 г</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -2366,18 +2361,18 @@
         </is>
       </c>
       <c r="D96" s="3" t="n">
-        <v>232.9</v>
+        <v>190.88</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Пакеты для мусора Liberhaus сверхпрочные с</t>
+          <t>Бананы 1кг</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Упаковка/прочее</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -2386,18 +2381,18 @@
         </is>
       </c>
       <c r="D97" s="3" t="n">
-        <v>232.72</v>
+        <v>188.49</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Творог Тема клубника, банан с 6 мес. 4.2%</t>
+          <t>Голубика 125г</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -2406,18 +2401,18 @@
         </is>
       </c>
       <c r="D98" s="3" t="n">
-        <v>230.93</v>
+        <v>187.99</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Творог Искренне Ваш 9% БЗМЖ 180г</t>
+          <t>Яблоки Гренни Смит</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -2426,18 +2421,18 @@
         </is>
       </c>
       <c r="D99" s="3" t="n">
-        <v>228.48</v>
+        <v>181.99</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Томаты Рост Медовые Черри оранжевые круглые</t>
+          <t>Колб.Сал.Итал.с/к нар150г</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -2446,18 +2441,18 @@
         </is>
       </c>
       <c r="D100" s="3" t="n">
-        <v>212.04</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>ОКСКОЕ Яйцо стол.2кат.10шт</t>
+          <t>Томаты Медовые черри красные круглые 200г</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Яйца</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -2466,18 +2461,18 @@
         </is>
       </c>
       <c r="D101" s="3" t="n">
-        <v>199.98</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Киви</t>
+          <t>Капуста квашеная</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -2486,18 +2481,18 @@
         </is>
       </c>
       <c r="D102" s="3" t="n">
-        <v>199</v>
+        <v>179.99</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Доставка H79963842837</t>
+          <t>Зефир Шармэль Ваниль 255г</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -2506,18 +2501,18 @@
         </is>
       </c>
       <c r="D103" s="3" t="n">
-        <v>199</v>
+        <v>179.65</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Сушки Семейка Озби ванильные 200г</t>
+          <t>Йогурт греческий Neo классический</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -2526,18 +2521,18 @@
         </is>
       </c>
       <c r="D104" s="3" t="n">
-        <v>198.93</v>
+        <v>173.19</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Конфеты ДаЁжъ с карамелью, арахисом и</t>
+          <t>Колбаса Останкино Салями Итальянская</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -2546,13 +2541,13 @@
         </is>
       </c>
       <c r="D105" s="3" t="n">
-        <v>193.8</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Кетчуп Heinz томатный 800г</t>
+          <t>Морковь</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -2566,18 +2561,18 @@
         </is>
       </c>
       <c r="D106" s="3" t="n">
-        <v>192.58</v>
+        <v>168.42</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Салат Айсберг Вкусвилл ~450 г</t>
+          <t>Йогурт Teos греческий</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -2586,18 +2581,18 @@
         </is>
       </c>
       <c r="D107" s="3" t="n">
-        <v>190.88</v>
+        <v>165.35</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Бананы 1кг</t>
+          <t>Лаваш для шаурмы Нижегородский хлеб</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -2606,18 +2601,18 @@
         </is>
       </c>
       <c r="D108" s="3" t="n">
-        <v>188.49</v>
+        <v>160</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Голубика 125г</t>
+          <t>Чай черный Выручай байховый крупнолистовой</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -2626,18 +2621,18 @@
         </is>
       </c>
       <c r="D109" s="3" t="n">
-        <v>187.99</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Творог мягкий 0% Савушкин</t>
+          <t>Салат Рукола Маркет Fresh</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -2646,18 +2641,18 @@
         </is>
       </c>
       <c r="D110" s="3" t="n">
-        <v>186.4</v>
+        <v>159.99</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Яблоки Гренни Смит</t>
+          <t>Молоко Простоквашино 1.5% БЗМЖ 930мл</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -2666,18 +2661,18 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>181.99</v>
+        <v>159.98</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Колб.Сал.Итал.с/к нар150г</t>
+          <t>Огурцы длинные</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2686,18 +2681,18 @@
         </is>
       </c>
       <c r="D112" s="3" t="n">
-        <v>179.99</v>
+        <v>159.96</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Томаты Медовые черри красные круглые 200г</t>
+          <t>Круассан 7Days</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -2706,13 +2701,13 @@
         </is>
       </c>
       <c r="D113" s="3" t="n">
-        <v>179.99</v>
+        <v>157.65</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Капуста квашеная с морковью Global Village 1000г</t>
+          <t>Томаты Черри на ветке 250г</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2726,18 +2721,18 @@
         </is>
       </c>
       <c r="D114" s="3" t="n">
-        <v>179.99</v>
+        <v>157.33</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Зефир Шармэль Ваниль 255г</t>
+          <t>Молоко Простоквашино питьевое</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -2746,19 +2741,18 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>179.65</v>
+        <v>154.99</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Йогурт греческий Neo
-классический</t>
+          <t>Соль Экстра йодированная выварочная 500г</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -2767,18 +2761,18 @@
         </is>
       </c>
       <c r="D116" s="3" t="n">
-        <v>173.19</v>
+        <v>154.98</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Колбаса Останкино Салями Итальянская</t>
+          <t>Сахар-песок Русский</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -2787,18 +2781,18 @@
         </is>
       </c>
       <c r="D117" s="3" t="n">
-        <v>169.99</v>
+        <v>154</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Морковь</t>
+          <t>Творог Савушкин Нежный мягкий</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -2807,18 +2801,18 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>168.42</v>
+        <v>153.34</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Йогурт Teos греческий 2% 250г</t>
+          <t>Рукола ВкусВилл 125 г</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -2827,19 +2821,18 @@
         </is>
       </c>
       <c r="D119" s="3" t="n">
-        <v>165.35</v>
+        <v>153.16</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Лаваш для шаурмы Нижегородский
-хлеб</t>
+          <t>Круассан 7 Days</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -2848,18 +2841,18 @@
         </is>
       </c>
       <c r="D120" s="3" t="n">
-        <v>160</v>
+        <v>152.41</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Чай черный Выручай байховый крупнолистовой</t>
+          <t>Ассорти зелени</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -2868,18 +2861,18 @@
         </is>
       </c>
       <c r="D121" s="3" t="n">
-        <v>159.99</v>
+        <v>152</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Салат Рукола Маркет Fresh, 125г</t>
+          <t>Жидкость Seasons для розжига 0.5л</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -2888,13 +2881,13 @@
         </is>
       </c>
       <c r="D122" s="3" t="n">
-        <v>159.99</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Молоко Простоквашино 1.5% БЗМЖ 930мл</t>
+          <t>Сметана Простоквашино</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -2908,18 +2901,18 @@
         </is>
       </c>
       <c r="D123" s="3" t="n">
-        <v>159.98</v>
+        <v>149.12</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Огурцы длинные, 1шт</t>
+          <t>Яйцо куриное Красная Цена С1 10шт.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -2928,18 +2921,18 @@
         </is>
       </c>
       <c r="D124" s="3" t="n">
-        <v>159.96</v>
+        <v>145.98</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Круассан 7Days с кремом Какао 4х65г</t>
+          <t>Творог Агуша клубника</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -2948,18 +2941,18 @@
         </is>
       </c>
       <c r="D125" s="3" t="n">
-        <v>157.65</v>
+        <v>143.36</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Томаты Черри на ветке 250г</t>
+          <t>Манго</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2968,18 +2961,18 @@
         </is>
       </c>
       <c r="D126" s="3" t="n">
-        <v>157.33</v>
+        <v>140.7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Молоко Простоквашино питьевое</t>
+          <t>Какао ЗОЛОТ.ЯРЛЫК порошок 100г</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -2988,18 +2981,18 @@
         </is>
       </c>
       <c r="D127" s="3" t="n">
-        <v>154.99</v>
+        <v>139.99</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Соль Экстра йодированная выварочная 500г</t>
+          <t>Пирожное Orion Choco Pie в глазури 12x30г</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3008,18 +3001,18 @@
         </is>
       </c>
       <c r="D128" s="3" t="n">
-        <v>154.98</v>
+        <v>139.99</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Сахар-песок Русский</t>
+          <t>Продукт рассольный Original Сиртаки</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -3028,13 +3021,13 @@
         </is>
       </c>
       <c r="D129" s="3" t="n">
-        <v>154</v>
+        <v>139</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Творог Савушкин Нежный мягкий 5% БЗМЖ</t>
+          <t>Сгущенное молоко Алексеевское цельное с сахаром 8,5% БЗМЖ 500 г</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3048,18 +3041,18 @@
         </is>
       </c>
       <c r="D130" s="3" t="n">
-        <v>153.34</v>
+        <v>138.03</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Рукола ВкусВилл 125 г</t>
+          <t>Сервисный сбор</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -3068,18 +3061,18 @@
         </is>
       </c>
       <c r="D131" s="3" t="n">
-        <v>153.16</v>
+        <v>138</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Круассан 7 Days с кремом какао, 4х65г</t>
+          <t>Сыр Вкус &amp; Польза Моцарелла шарики</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3088,18 +3081,18 @@
         </is>
       </c>
       <c r="D132" s="3" t="n">
-        <v>152.41</v>
+        <v>136.99</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Ассорти зелени</t>
+          <t>Попкорн для СВЧ солёный</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -3108,18 +3101,18 @@
         </is>
       </c>
       <c r="D133" s="3" t="n">
-        <v>152</v>
+        <v>134.81</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Жидкость Seasons для розжига 0.5л</t>
+          <t>Батон Черемушки нарезка 400г</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -3128,18 +3121,18 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>149.99</v>
+        <v>133.98</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Сметана Простоквашино 20% БЗМЖ 300г</t>
+          <t>Яблоки красные Крымские ~780 г</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -3148,18 +3141,18 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>149.12</v>
+        <v>132.94</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Яйцо куриное Красная Цена С1 10шт.</t>
+          <t>Зелёный горошек</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -3168,18 +3161,18 @@
         </is>
       </c>
       <c r="D136" s="3" t="n">
-        <v>145.98</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Творог Агуша клубника</t>
+          <t>Десерт ФрутоНяня Яблоко, банан, клубника</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -3188,18 +3181,18 @@
         </is>
       </c>
       <c r="D137" s="3" t="n">
-        <v>143.36</v>
+        <v>131.41</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Яйцо С1 Из Лавки</t>
+          <t>Чай зеленый Принцесса Ява Традиционный</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Яйца</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -3208,18 +3201,18 @@
         </is>
       </c>
       <c r="D138" s="3" t="n">
-        <v>142</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Манго спелое 1кг</t>
+          <t>Чай черный Майский Корона Российской</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -3228,18 +3221,18 @@
         </is>
       </c>
       <c r="D139" s="3" t="n">
-        <v>140.7</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Какао ЗОЛОТ.ЯРЛЫК порошок 100г</t>
+          <t>Печенье Шарлиз</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -3248,18 +3241,18 @@
         </is>
       </c>
       <c r="D140" s="3" t="n">
-        <v>139.99</v>
+        <v>129.99</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Пирожное Orion Choco Pie в глазури 12x30г</t>
+          <t>Макароны Makfa Спагетти 450г</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -3268,19 +3261,18 @@
         </is>
       </c>
       <c r="D141" s="3" t="n">
-        <v>139.99</v>
+        <v>128.34</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Продукт рассольный Original
-Сиртаки</t>
+          <t>Печенье овсяное Классическое Посиделкино 103.00 1.000 НДС 22% 103.00 https://check.yandex.ru/?fn=7380440801461798&amp;fpd=1941284702&amp;n=118449 29.06.2026, 11:46 Стр. 1</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3289,19 +3281,18 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Сгущенное молоко Алексеевское цельное с сахаром 8,5% БЗМЖ
-500 г</t>
+          <t>Томаты ФЛАМЕНКО сливовидные 1кг</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3310,18 +3301,18 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>138.03</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Сервисный сбор</t>
+          <t>Яйцо куриное Окское столовое С1</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3330,18 +3321,18 @@
         </is>
       </c>
       <c r="D144" s="3" t="n">
-        <v>138</v>
+        <v>124.99</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Сыр Вкус &amp; Польза Моцарелла шарики 45%</t>
+          <t>Пломбир Станция Молочная ванильный</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3350,19 +3341,18 @@
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>136.99</v>
+        <v>124.99</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Попкорн для СВЧ солёный Из
-Лавки</t>
+          <t>Чай Richard Королевский цейлон черный</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3371,18 +3361,18 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>134.81</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Батон Черемушки нарезка 400г</t>
+          <t>Молоко Красная цена питьевое</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3391,18 +3381,18 @@
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>133.98</v>
+        <v>119.97</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Яблоки красные Крымские ~780 г</t>
+          <t>Помидоры красные ~530 г</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3411,18 +3401,18 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>132.94</v>
+        <v>119.75</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Зелёный горошек Из Лавки</t>
+          <t>Биолакт Тёма сладкий</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3431,18 +3421,18 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>132.3</v>
+        <v>118.61</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Десерт ФрутоНяня Яблоко, банан, клубника с 7</t>
+          <t>Картофель</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3451,18 +3441,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>131.41</v>
+        <v>117.34</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Чай зеленый Принцесса Ява Традиционный</t>
+          <t>Масло подсолнечное Слобода</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3471,18 +3461,18 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>129.99</v>
+        <v>117.22</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Чай черный Майский Корона Российской</t>
+          <t>Киви спелые 3 шт</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3491,18 +3481,18 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>129.99</v>
+        <v>116.57</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Печенье Шарлиз Классическое овсяное</t>
+          <t>Кукуруза консервированная Бондюэль</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -3511,18 +3501,18 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>129.99</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Макароны Makfa Спагетти 450г</t>
+          <t>Огурцы корнишоны премиум</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3531,27 +3521,18 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>128.34</v>
+        <v>114.07</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Печенье овсяное Классическое
-Посиделкино
-103.00
-1.000
-НДС
-22%
-103.00
-https://check.yandex.ru/?fn=7380440801461798&amp;fpd=1941284702&amp;n=118449
-29.06.2026, 11:46
-Стр. 1 из 2</t>
+          <t>Пакеты Liberhaus фасовочные 30х40см 100шт.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Упаковка/прочее</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3560,18 +3541,18 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>128</v>
+        <v>113.55</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Манго спелое</t>
+          <t>Огурцы среднеплодные</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3580,18 +3561,18 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>127.28</v>
+        <v>110.59</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Томаты ФЛАМЕНКО сливовидные 1кг</t>
+          <t>Нектар Soko Grande Premium тыквенный с</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3600,18 +3581,18 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>126.9</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Яйцо куриное Окское столовое С1, 10шт</t>
+          <t>Печенье Посиделкино Овсяное</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3620,18 +3601,18 @@
         </is>
       </c>
       <c r="D158" s="3" t="n">
-        <v>124.99</v>
+        <v>110.49</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Пломбир Станция Молочная ванильный 12%</t>
+          <t>Чай зеленый Assand Chinese Green листовой 100г</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -3640,18 +3621,18 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>124.99</v>
+        <v>110.49</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Чай Richard Королевский цейлон черный</t>
+          <t>Шампиньоны резаные замороженные 400 г</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3660,13 +3641,13 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>119.99</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Молоко Красная цена питьевое 1% БЗМЖ</t>
+          <t>Сметана</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3680,18 +3661,18 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>119.97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Помидоры красные ~530 г</t>
+          <t>Творог Тема</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -3700,13 +3681,13 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>119.75</v>
+        <v>107.97</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Биолакт Тёма сладкий с 8 месяцев 3.2%, 208г</t>
+          <t>Молоко</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3720,18 +3701,18 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>118.61</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Картофель</t>
+          <t>Творог Дмитровский МЗ</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3740,18 +3721,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>117.34</v>
+        <v>106.26</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Масло подсолнечное Слобода</t>
+          <t>Имбирь</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3760,13 +3741,13 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>117.22</v>
+        <v>104.99</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Киви спелые 3 шт</t>
+          <t>Лимон</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -3780,18 +3761,18 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>116.57</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Кукуруза консервированная Бондюэль</t>
+          <t>Кефир Станция Молочная 3.2% БЗМЖ 930г</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -3800,18 +3781,18 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>114.99</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Огурцы корнишоны премиум, 300г</t>
+          <t>Творог Савушкин нежный мягкий</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -3820,18 +3801,18 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>114.07</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Пакеты Liberhaus фасовочные 30х40см 100шт.</t>
+          <t>Творог 5% Из молока нашей 99.00 1 НДС 99.00 https://check.yandex.ru/?fn=7380440801483769&amp;fpd=4081801637&amp;n=135982 29.06.2026, 11:57 Стр. 1 из 4 дойки</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Упаковка/прочее</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3840,18 +3821,18 @@
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>113.55</v>
+        <v>99</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Огурцы среднеплодные</t>
+          <t>Сметана Домик в деревне</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3860,18 +3841,18 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>110.59</v>
+        <v>94.98999999999999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Нектар Soko Grande Premium тыквенный с</t>
+          <t>Конфеты Рот Фронт Батончики 250г</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3880,18 +3861,18 @@
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>110.57</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Печенье Посиделкино Овсяное классическое 320г</t>
+          <t>Набор пасхальный Seasons Классический для</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3900,18 +3881,18 @@
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>110.49</v>
+        <v>90.98999999999999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Чай зеленый Assand Chinese Green листовой 100г</t>
+          <t>Халва Азовская АФ Царская подсолнечная на</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3920,13 +3901,13 @@
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>110.49</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Шампиньоны резаные замороженные 400 г</t>
+          <t>Морковь мытая Маркет Fresh</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -3940,18 +3921,18 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>109.75</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Сметана 15% Из Лавки</t>
+          <t>Соль Salina пищевая каменная 1кг</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3960,13 +3941,13 @@
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>109</v>
+        <v>89.18000000000001</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Творог Тема с 6 мес. 5% 95г</t>
+          <t>Творог мягкий детский Тема</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -3980,18 +3961,18 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>107.97</v>
+        <v>88.78</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Молоко сгущённое Алексеевское цельное с</t>
+          <t>Творожная масса</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -4000,18 +3981,18 @@
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>107.1</v>
+        <v>87</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Творог Дмитровский МЗ 9% БЗМЖ 180г</t>
+          <t>Лук репчатый</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4020,18 +4001,18 @@
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>106.26</v>
+        <v>84.89</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Имбирь Global Village маринованный розовый</t>
+          <t>Картофель Бэби ~1</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -4040,18 +4021,18 @@
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>104.99</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Лимон</t>
+          <t>Творог Простоквашино</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -4060,18 +4041,18 @@
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>102.92</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Кефир Станция Молочная 3.2% БЗМЖ 930г</t>
+          <t>Петрушка</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4080,13 +4061,13 @@
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>99.98999999999999</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Творог Савушкин нежный мягкий 0% 125г</t>
+          <t>Молоко Станция Молочная 3.3-6.0% БЗМЖ</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4100,26 +4081,18 @@
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>99.98</v>
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Творог 5% Из молока нашей
-99.00
-1
-НДС
-99.00
-https://check.yandex.ru/?fn=7380440801483769&amp;fpd=4081801637&amp;n=135982
-29.06.2026, 11:57
-Стр. 1 из 4
-дойки</t>
+          <t>Макаронные изделия Barilla Баветте №13 из</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4128,13 +4101,13 @@
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>99</v>
+        <v>80.73999999999999</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>Творог Савушкин Нежный мягкий 5%, 125г</t>
+          <t>А.РОС.Сырок тв.гл.м.ш.мол.сг50г</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4148,18 +4121,18 @@
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>97.98</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Сметана 15% Сливочная Экомилк</t>
+          <t>Лаваш тонкий Коломенское армянский 360г</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4168,13 +4141,13 @@
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>95</v>
+        <v>75.27</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Сметана Домик в деревне 20%, 300г</t>
+          <t>Творог Станция Молочная</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4188,18 +4161,18 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>94.98999999999999</v>
+        <v>74.98999999999999</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Конфеты Рот Фронт Батончики 250г</t>
+          <t>Помидоры</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4208,18 +4181,18 @@
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>93.78</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Набор пасхальный Seasons Классический для</t>
+          <t>Персики плоские Турция</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4228,18 +4201,18 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>90.98999999999999</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Халва Азовская АФ Царская подсолнечная на</t>
+          <t>Яблоки сезонные</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4248,18 +4221,18 @@
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>90.09</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Морковь мытая Маркет Fresh, 1кг</t>
+          <t>Творог</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4268,18 +4241,18 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>89.98999999999999</v>
+        <v>70.02</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Соль Salina пищевая каменная 1кг</t>
+          <t>Попкорн для СВЧ</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4288,18 +4261,18 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>89.18000000000001</v>
+        <v>70</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Творог мягкий детский Тема с 6 месяцев 5% БЗМЖ 95 г</t>
+          <t>Киви крупное Из Лавки 242.00 1 НДС 242.00 https://check.yandex.ru/?fn=7380440801484133&amp;fpd=869598089&amp;n=195435 29.06.2026, 11:57 Стр. 1</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4308,14 +4281,13 @@
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>88.78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Творожная масса с курагой Из
-Лавки</t>
+          <t>Набор пасхальный Домашняя кухня</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4329,18 +4301,18 @@
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>87</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Печенье Посиделкино Овсяное классическое</t>
+          <t>Картофель в сетке ~2</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -4349,18 +4321,18 @@
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>84.98999999999999</v>
+        <v>68.98999999999999</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Йогурт Простоквашино Греческий 2% 135г</t>
+          <t>Батон Коломенское Нарезной</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4369,18 +4341,18 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>84.98</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Лук репчатый</t>
+          <t>Яблоки Красная цена фасованные</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4389,13 +4361,13 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>84.89</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Картофель Бэби ~1,04 кг</t>
+          <t>Огурцы Ботаника 420 г</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4409,18 +4381,18 @@
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>82.54000000000001</v>
+        <v>62.39</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Творог Простоквашино 5%, 200г</t>
+          <t>Печенье Мария Любятово</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4429,18 +4401,18 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>82.38</v>
+        <v>62.24</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Сметана 15% Пр!ст, 300г</t>
+          <t>Попкорн Mixbar Party</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4449,18 +4421,18 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>81.98999999999999</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Петрушка Global Village 100г</t>
+          <t>Горчица Красная цена Столовая острая 150г</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4469,18 +4441,18 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>81.95</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Молоко Станция Молочная 3.3-6.0% БЗМЖ</t>
+          <t>Рис круглозернистый шлифованный 900г</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -4489,18 +4461,18 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>80.98999999999999</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Макаронные изделия Barilla Баветте №13 из</t>
+          <t>Хлебцы Щедрые ржаные 100г</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4509,18 +4481,18 @@
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>80.73999999999999</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>А.РОС.Сырок тв.гл.м.ш.мол.сг50г</t>
+          <t>Булочки Коломенский пшеничные</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4529,18 +4501,18 @@
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>79.98999999999999</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Лаваш тонкий Коломенское армянский 360г</t>
+          <t>Макароны Makfa витки 450г</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4549,18 +4521,18 @@
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>75.27</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Творог Станция Молочная 5% БЗМЖ 180г</t>
+          <t>Макароны Makfa спирали экспресс 400г</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4569,13 +4541,13 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>74.98999999999999</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Помидоры</t>
+          <t>Огурцы среднеплодные 1кг</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4589,18 +4561,18 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>71.98999999999999</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Персики плоские Турция</t>
+          <t>Яйцо С2</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Яйца</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4609,18 +4581,18 @@
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>70.19</v>
+        <v>55</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Яблоки сезонные</t>
+          <t>Морковь отечественная</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4629,13 +4601,13 @@
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>70.19</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Творог 5% Молочный знак, 180г</t>
+          <t>Снежок ФрутоНяня</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4649,18 +4621,18 @@
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>70.02</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Попкорн для СВЧ солёный Из Лавки</t>
+          <t>Печенье детское Бегемотик Бонди кальций</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4669,25 +4641,18 @@
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Киви крупное Из Лавки
-242.00
-1
-НДС
-242.00
-https://check.yandex.ru/?fn=7380440801484133&amp;fpd=869598089&amp;n=195435
-29.06.2026, 11:57
-Стр. 1 из 3</t>
+          <t>Печенье Юбилейное</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4696,18 +4661,18 @@
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>70</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Набор пасхальный Домашняя кухня</t>
+          <t>Яблоки фасованные ~1</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4716,18 +4681,18 @@
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>69.98999999999999</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Картофель в сетке ~2,3 кг</t>
+          <t>Творог мягкий Искренне Ваш</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4736,13 +4701,13 @@
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>68.98999999999999</v>
+        <v>50.99</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Батон Коломенское Нарезной, 400г</t>
+          <t>Батон Хлебный Дом Звездный нарезка 350г</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4756,18 +4721,18 @@
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>68.37</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Яблоки Красная цена фасованные</t>
+          <t>Творог Простоквашино Нежный мягкий</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4776,13 +4741,13 @@
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>65.70999999999999</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Огурцы Ботаника 420 г</t>
+          <t>Огурцы гладкие ~450 г</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -4796,18 +4761,18 @@
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>62.39</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Печенье Мария Любятово</t>
+          <t>Макаронные изделия Barilla Пенне Ригате №73 из</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4816,18 +4781,18 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>62.24</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Попкорн Mixbar Party соленый 100г</t>
+          <t>Пюре ФрутоНяня Салатик</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4836,18 +4801,18 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>61.99</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Горчица Красная цена Столовая острая 150г</t>
+          <t>Пюре ФрутоНяня Яблоко, банан, груша с</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -4856,18 +4821,18 @@
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>61.98</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Рис круглозернистый шлифованный 900г</t>
+          <t>Капуста белокочанная</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4876,18 +4841,18 @@
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>60.8</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Хлебцы Щедрые ржаные 100г</t>
+          <t>Молоко сгущённое с сахаром Алексеевское</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4896,18 +4861,18 @@
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>59.99</v>
+        <v>45</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Булочки Коломенский пшеничные с кунжутом</t>
+          <t>Апельсины</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -4916,18 +4881,18 @@
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>57.99</v>
+        <v>43.79</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Макароны Makfa витки 450г</t>
+          <t>Печенье Любятово Мария традиционное</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4936,18 +4901,18 @@
         </is>
       </c>
       <c r="D223" s="3" t="n">
-        <v>57.76</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Макароны Makfa спирали экспресс 400г</t>
+          <t>Печенье Honey Kid Детское</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -4956,18 +4921,18 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>57.76</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Огурцы среднеплодные 1кг</t>
+          <t>Манго жёлтое</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4976,18 +4941,18 @@
         </is>
       </c>
       <c r="D225" s="3" t="n">
-        <v>56.65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Яйцо С2</t>
+          <t>Батон Мосхлеб нарезной</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Яйца</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4996,18 +4961,18 @@
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Морковь отечественная</t>
+          <t>Печенье Коломенское Овсяное злаковое</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -5016,18 +4981,18 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>54.28</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Снежок ФрутоНяня с клубникой и земляникой с</t>
+          <t>Батон Селяночка Нарезной нарезка 400г</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5036,18 +5001,18 @@
         </is>
       </c>
       <c r="D228" s="3" t="n">
-        <v>53.99</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Сметана 15% Простоквашино БЗМЖ 300 г</t>
+          <t>Кисель ФрутоНяня клубника-малина</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5056,19 +5021,18 @@
         </is>
       </c>
       <c r="D229" s="3" t="n">
-        <v>53.99</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Печенье детское Бегемотик
-Бонди кальций</t>
+          <t>Свекла ВкусВилл ~760 г</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5077,18 +5041,18 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>53</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Печенье Юбилейное с овсяными хлопьями</t>
+          <t>Соль поваренная пищевая мелкая 1кг</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5097,18 +5061,18 @@
         </is>
       </c>
       <c r="D231" s="3" t="n">
-        <v>52.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Яблоки фасованные ~1,2 кг</t>
+          <t>Гречка ядрица 900г</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5117,18 +5081,18 @@
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>52.72</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Творог мягкий Искренне Ваш 9% БЗМЖ 180 г</t>
+          <t>Хлеб Красная Цена Белый 380г</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5137,18 +5101,18 @@
         </is>
       </c>
       <c r="D233" s="3" t="n">
-        <v>50.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Батон Хлебный Дом Звездный нарезка 350г</t>
+          <t>Свекла</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5157,18 +5121,18 @@
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>50.93</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Творог Простоквашино Нежный мягкий 5%,</t>
+          <t>Пакет ПЯТЕРОЧКА 65х40см</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Упаковка/прочее</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5177,18 +5141,18 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>50.25</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Огурцы гладкие ~450 г</t>
+          <t>Мешки для мусора</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -5197,18 +5161,18 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>49.72</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Макаронные изделия Barilla Пенне Ригате №73 из</t>
+          <t>Лаки Миши в ассортименте</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5217,18 +5181,18 @@
         </is>
       </c>
       <c r="D237" s="3" t="n">
-        <v>48.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>Пюре ФрутоНяня Салатик из фруктов с 6 мес. 90г</t>
+          <t>Доставка H99979765568</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -5237,18 +5201,18 @@
         </is>
       </c>
       <c r="D238" s="3" t="n">
-        <v>46.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
         <is>
-          <t>Пюре ФрутоНяня Яблоко, банан, груша с</t>
+          <t>Сборка</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -5257,18 +5221,18 @@
         </is>
       </c>
       <c r="D239" s="3" t="n">
-        <v>46.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>Капуста белокочанная</t>
+          <t>Игрушка АМНЯМАНИЯ 2 в ассортименте</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -5277,407 +5241,6 @@
         </is>
       </c>
       <c r="D240" s="3" t="n">
-        <v>46.96</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>Молоко сгущённое с сахаром
-Алексеевское</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Молочные продукты</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D241" s="3" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>Апельсины</t>
-        </is>
-      </c>
-      <c r="B242" t="inlineStr">
-        <is>
-          <t>Фрукты и ягоды</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D242" s="3" t="n">
-        <v>43.79</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>Печенье Любятово Мария традиционное</t>
-        </is>
-      </c>
-      <c r="B243" t="inlineStr">
-        <is>
-          <t>Сладости и снеки</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D243" s="3" t="n">
-        <v>42.99</v>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>Печенье Honey Kid Детское с 6 мес. 60г</t>
-        </is>
-      </c>
-      <c r="B244" t="inlineStr">
-        <is>
-          <t>Сладости и снеки</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D244" s="3" t="n">
-        <v>38.24</v>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>Манго жёлтое</t>
-        </is>
-      </c>
-      <c r="B245" t="inlineStr">
-        <is>
-          <t>Фрукты и ягоды</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D245" s="3" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>Батон Мосхлеб нарезной</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Хлеб и выпечка</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D246" s="3" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>Печенье Коломенское Овсяное злаковое</t>
-        </is>
-      </c>
-      <c r="B247" t="inlineStr">
-        <is>
-          <t>Сладости и снеки</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D247" s="3" t="n">
-        <v>37.2</v>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>Батон Селяночка Нарезной нарезка 400г</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Хлеб и выпечка</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D248" s="3" t="n">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>Кисель ФрутоНяня клубника-малина с 12</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>Фрукты и ягоды</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D249" s="3" t="n">
-        <v>31.5</v>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>Свекла ВкусВилл ~760 г</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>Овощи и зелень</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D250" s="3" t="n">
-        <v>23.94</v>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>Соль поваренная пищевая мелкая 1кг</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>Бакалея и специи</t>
-        </is>
-      </c>
-      <c r="C251" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D251" s="3" t="n">
-        <v>22.99</v>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>Гречка ядрица 900г</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Крупы и макароны</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D252" s="3" t="n">
-        <v>20.16</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>Хлеб Красная Цена Белый 380г</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>Хлеб и выпечка</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D253" s="3" t="n">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>Свекла</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Овощи и зелень</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D254" s="3" t="n">
-        <v>18.24</v>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>Пакет ПЯТЕРОЧКА 65х40см</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>Упаковка/прочее</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D255" s="3" t="n">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>Мешки для мусора с завязками 60л Маркет,</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D256" s="3" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>Лаки Миши в ассортименте, 1шт</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D257" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>Доставка H99979765568</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D258" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>Сборка</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D259" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>Игрушка АМНЯМАНИЯ 2 в ассортименте, 1 шт.</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>Фрукты и ягоды</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D260" s="3" t="n">
         <v>0</v>
       </c>
     </row>

--- a/products to monitor.xlsx
+++ b/products to monitor.xlsx
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D240"/>
+  <dimension ref="A1:D237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -3267,12 +3267,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Печенье овсяное Классическое Посиделкино 103.00 1.000 НДС 22% 103.00 https://check.yandex.ru/?fn=7380440801461798&amp;fpd=1941284702&amp;n=118449 29.06.2026, 11:46 Стр. 1</t>
+          <t>Томаты ФЛАМЕНКО сливовидные 1кг</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -3281,18 +3281,18 @@
         </is>
       </c>
       <c r="D142" s="3" t="n">
-        <v>128</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Томаты ФЛАМЕНКО сливовидные 1кг</t>
+          <t>Яйцо куриное Окское столовое С1</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Мясо и птица</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -3301,18 +3301,18 @@
         </is>
       </c>
       <c r="D143" s="3" t="n">
-        <v>126.9</v>
+        <v>124.99</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Яйцо куриное Окское столовое С1</t>
+          <t>Пломбир Станция Молочная ванильный</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Мясо и птица</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -3327,12 +3327,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Пломбир Станция Молочная ванильный</t>
+          <t>Чай Richard Королевский цейлон черный</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Напитки / чай / кофе</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -3341,18 +3341,18 @@
         </is>
       </c>
       <c r="D145" s="3" t="n">
-        <v>124.99</v>
+        <v>119.99</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Чай Richard Королевский цейлон черный</t>
+          <t>Молоко Красная цена питьевое</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Напитки / чай / кофе</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -3361,18 +3361,18 @@
         </is>
       </c>
       <c r="D146" s="3" t="n">
-        <v>119.99</v>
+        <v>119.97</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Молоко Красная цена питьевое</t>
+          <t>Помидоры красные ~530 г</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -3381,18 +3381,18 @@
         </is>
       </c>
       <c r="D147" s="3" t="n">
-        <v>119.97</v>
+        <v>119.75</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Помидоры красные ~530 г</t>
+          <t>Биолакт Тёма сладкий</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -3401,18 +3401,18 @@
         </is>
       </c>
       <c r="D148" s="3" t="n">
-        <v>119.75</v>
+        <v>118.61</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Биолакт Тёма сладкий</t>
+          <t>Картофель</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -3421,18 +3421,18 @@
         </is>
       </c>
       <c r="D149" s="3" t="n">
-        <v>118.61</v>
+        <v>117.34</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Картофель</t>
+          <t>Масло подсолнечное Слобода</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -3441,18 +3441,18 @@
         </is>
       </c>
       <c r="D150" s="3" t="n">
-        <v>117.34</v>
+        <v>117.22</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Масло подсолнечное Слобода</t>
+          <t>Киви спелые 3 шт</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -3461,18 +3461,18 @@
         </is>
       </c>
       <c r="D151" s="3" t="n">
-        <v>117.22</v>
+        <v>116.57</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Киви спелые 3 шт</t>
+          <t>Кукуруза консервированная Бондюэль</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -3481,13 +3481,13 @@
         </is>
       </c>
       <c r="D152" s="3" t="n">
-        <v>116.57</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Кукуруза консервированная Бондюэль</t>
+          <t>Огурцы корнишоны премиум</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3501,18 +3501,18 @@
         </is>
       </c>
       <c r="D153" s="3" t="n">
-        <v>114.99</v>
+        <v>114.07</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Огурцы корнишоны премиум</t>
+          <t>Пакеты Liberhaus фасовочные 30х40см 100шт.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Упаковка/прочее</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -3521,18 +3521,18 @@
         </is>
       </c>
       <c r="D154" s="3" t="n">
-        <v>114.07</v>
+        <v>113.55</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Пакеты Liberhaus фасовочные 30х40см 100шт.</t>
+          <t>Огурцы среднеплодные</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Упаковка/прочее</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -3541,18 +3541,18 @@
         </is>
       </c>
       <c r="D155" s="3" t="n">
-        <v>113.55</v>
+        <v>110.59</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Огурцы среднеплодные</t>
+          <t>Нектар Soko Grande Premium тыквенный с</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -3561,18 +3561,18 @@
         </is>
       </c>
       <c r="D156" s="3" t="n">
-        <v>110.59</v>
+        <v>110.57</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Нектар Soko Grande Premium тыквенный с</t>
+          <t>Печенье Посиделкино Овсяное</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3581,18 +3581,18 @@
         </is>
       </c>
       <c r="D157" s="3" t="n">
-        <v>110.57</v>
+        <v>110.49</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Печенье Посиделкино Овсяное</t>
+          <t>Чай зеленый Assand Chinese Green листовой 100г</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -3607,7 +3607,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Чай зеленый Assand Chinese Green листовой 100г</t>
+          <t>Шампиньоны резаные замороженные 400 г</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -3621,18 +3621,18 @@
         </is>
       </c>
       <c r="D159" s="3" t="n">
-        <v>110.49</v>
+        <v>109.75</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Шампиньоны резаные замороженные 400 г</t>
+          <t>Сметана</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -3641,13 +3641,13 @@
         </is>
       </c>
       <c r="D160" s="3" t="n">
-        <v>109.75</v>
+        <v>109</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Сметана</t>
+          <t>Творог Тема</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -3661,13 +3661,13 @@
         </is>
       </c>
       <c r="D161" s="3" t="n">
-        <v>109</v>
+        <v>107.97</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Творог Тема</t>
+          <t>Молоко</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -3681,13 +3681,13 @@
         </is>
       </c>
       <c r="D162" s="3" t="n">
-        <v>107.97</v>
+        <v>107.1</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Молоко</t>
+          <t>Творог Дмитровский МЗ</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -3701,18 +3701,18 @@
         </is>
       </c>
       <c r="D163" s="3" t="n">
-        <v>107.1</v>
+        <v>106.26</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Творог Дмитровский МЗ</t>
+          <t>Имбирь</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -3721,18 +3721,18 @@
         </is>
       </c>
       <c r="D164" s="3" t="n">
-        <v>106.26</v>
+        <v>104.99</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>Имбирь</t>
+          <t>Лимон</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -3741,18 +3741,18 @@
         </is>
       </c>
       <c r="D165" s="3" t="n">
-        <v>104.99</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>Лимон</t>
+          <t>Кефир Станция Молочная 3.2% БЗМЖ 930г</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -3761,13 +3761,13 @@
         </is>
       </c>
       <c r="D166" s="3" t="n">
-        <v>102.92</v>
+        <v>99.98999999999999</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>Кефир Станция Молочная 3.2% БЗМЖ 930г</t>
+          <t>Творог Савушкин нежный мягкий</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -3781,13 +3781,13 @@
         </is>
       </c>
       <c r="D167" s="3" t="n">
-        <v>99.98999999999999</v>
+        <v>99.98</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>Творог Савушкин нежный мягкий</t>
+          <t>Сметана Домик в деревне</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -3801,18 +3801,18 @@
         </is>
       </c>
       <c r="D168" s="3" t="n">
-        <v>99.98</v>
+        <v>94.98999999999999</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>Творог 5% Из молока нашей 99.00 1 НДС 99.00 https://check.yandex.ru/?fn=7380440801483769&amp;fpd=4081801637&amp;n=135982 29.06.2026, 11:57 Стр. 1 из 4 дойки</t>
+          <t>Конфеты Рот Фронт Батончики 250г</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -3821,18 +3821,18 @@
         </is>
       </c>
       <c r="D169" s="3" t="n">
-        <v>99</v>
+        <v>93.78</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>Сметана Домик в деревне</t>
+          <t>Набор пасхальный Seasons Классический для</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -3841,18 +3841,18 @@
         </is>
       </c>
       <c r="D170" s="3" t="n">
-        <v>94.98999999999999</v>
+        <v>90.98999999999999</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>Конфеты Рот Фронт Батончики 250г</t>
+          <t>Халва Азовская АФ Царская подсолнечная на</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -3861,18 +3861,18 @@
         </is>
       </c>
       <c r="D171" s="3" t="n">
-        <v>93.78</v>
+        <v>90.09</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>Набор пасхальный Seasons Классический для</t>
+          <t>Морковь мытая Маркет Fresh</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -3881,18 +3881,18 @@
         </is>
       </c>
       <c r="D172" s="3" t="n">
-        <v>90.98999999999999</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>Халва Азовская АФ Царская подсолнечная на</t>
+          <t>Соль Salina пищевая каменная 1кг</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -3901,18 +3901,18 @@
         </is>
       </c>
       <c r="D173" s="3" t="n">
-        <v>90.09</v>
+        <v>89.18000000000001</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>Морковь мытая Маркет Fresh</t>
+          <t>Творог мягкий детский Тема</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -3921,18 +3921,18 @@
         </is>
       </c>
       <c r="D174" s="3" t="n">
-        <v>89.98999999999999</v>
+        <v>88.78</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>Соль Salina пищевая каменная 1кг</t>
+          <t>Творожная масса</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -3941,18 +3941,18 @@
         </is>
       </c>
       <c r="D175" s="3" t="n">
-        <v>89.18000000000001</v>
+        <v>87</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>Творог мягкий детский Тема</t>
+          <t>Лук репчатый</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -3961,18 +3961,18 @@
         </is>
       </c>
       <c r="D176" s="3" t="n">
-        <v>88.78</v>
+        <v>84.89</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>Творожная масса</t>
+          <t>Картофель Бэби ~1</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -3981,18 +3981,18 @@
         </is>
       </c>
       <c r="D177" s="3" t="n">
-        <v>87</v>
+        <v>82.54000000000001</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>Лук репчатый</t>
+          <t>Творог Простоквашино</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -4001,13 +4001,13 @@
         </is>
       </c>
       <c r="D178" s="3" t="n">
-        <v>84.89</v>
+        <v>82.38</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>Картофель Бэби ~1</t>
+          <t>Петрушка</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4021,13 +4021,13 @@
         </is>
       </c>
       <c r="D179" s="3" t="n">
-        <v>82.54000000000001</v>
+        <v>81.95</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>Творог Простоквашино</t>
+          <t>Молоко Станция Молочная 3.3-6.0% БЗМЖ</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4041,18 +4041,18 @@
         </is>
       </c>
       <c r="D180" s="3" t="n">
-        <v>82.38</v>
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>Петрушка</t>
+          <t>Макаронные изделия Barilla Баветте №13 из</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -4061,13 +4061,13 @@
         </is>
       </c>
       <c r="D181" s="3" t="n">
-        <v>81.95</v>
+        <v>80.73999999999999</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>Молоко Станция Молочная 3.3-6.0% БЗМЖ</t>
+          <t>А.РОС.Сырок тв.гл.м.ш.мол.сг50г</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4081,18 +4081,18 @@
         </is>
       </c>
       <c r="D182" s="3" t="n">
-        <v>80.98999999999999</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>Макаронные изделия Barilla Баветте №13 из</t>
+          <t>Лаваш тонкий Коломенское армянский 360г</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -4101,13 +4101,13 @@
         </is>
       </c>
       <c r="D183" s="3" t="n">
-        <v>80.73999999999999</v>
+        <v>75.27</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>А.РОС.Сырок тв.гл.м.ш.мол.сг50г</t>
+          <t>Творог Станция Молочная</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4121,18 +4121,18 @@
         </is>
       </c>
       <c r="D184" s="3" t="n">
-        <v>79.98999999999999</v>
+        <v>74.98999999999999</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>Лаваш тонкий Коломенское армянский 360г</t>
+          <t>Помидоры</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -4141,18 +4141,18 @@
         </is>
       </c>
       <c r="D185" s="3" t="n">
-        <v>75.27</v>
+        <v>71.98999999999999</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>Творог Станция Молочная</t>
+          <t>Персики плоские Турция</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -4161,18 +4161,18 @@
         </is>
       </c>
       <c r="D186" s="3" t="n">
-        <v>74.98999999999999</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>Помидоры</t>
+          <t>Яблоки сезонные</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -4181,18 +4181,18 @@
         </is>
       </c>
       <c r="D187" s="3" t="n">
-        <v>71.98999999999999</v>
+        <v>70.19</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>Персики плоские Турция</t>
+          <t>Творог</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -4201,18 +4201,18 @@
         </is>
       </c>
       <c r="D188" s="3" t="n">
-        <v>70.19</v>
+        <v>70.02</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>Яблоки сезонные</t>
+          <t>Попкорн для СВЧ</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -4221,18 +4221,18 @@
         </is>
       </c>
       <c r="D189" s="3" t="n">
-        <v>70.19</v>
+        <v>70</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>Творог</t>
+          <t>Набор пасхальный Домашняя кухня</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -4241,18 +4241,18 @@
         </is>
       </c>
       <c r="D190" s="3" t="n">
-        <v>70.02</v>
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>Попкорн для СВЧ</t>
+          <t>Картофель в сетке ~2</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -4261,18 +4261,18 @@
         </is>
       </c>
       <c r="D191" s="3" t="n">
-        <v>70</v>
+        <v>68.98999999999999</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>Киви крупное Из Лавки 242.00 1 НДС 242.00 https://check.yandex.ru/?fn=7380440801484133&amp;fpd=869598089&amp;n=195435 29.06.2026, 11:57 Стр. 1</t>
+          <t>Батон Коломенское Нарезной</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -4281,18 +4281,18 @@
         </is>
       </c>
       <c r="D192" s="3" t="n">
-        <v>70</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>Набор пасхальный Домашняя кухня</t>
+          <t>Яблоки Красная цена фасованные</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -4301,13 +4301,13 @@
         </is>
       </c>
       <c r="D193" s="3" t="n">
-        <v>69.98999999999999</v>
+        <v>65.70999999999999</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>Картофель в сетке ~2</t>
+          <t>Огурцы Ботаника 420 г</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4321,18 +4321,18 @@
         </is>
       </c>
       <c r="D194" s="3" t="n">
-        <v>68.98999999999999</v>
+        <v>62.39</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>Батон Коломенское Нарезной</t>
+          <t>Печенье Мария Любятово</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -4341,18 +4341,18 @@
         </is>
       </c>
       <c r="D195" s="3" t="n">
-        <v>68.37</v>
+        <v>62.24</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>Яблоки Красная цена фасованные</t>
+          <t>Попкорн Mixbar Party</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4361,18 +4361,18 @@
         </is>
       </c>
       <c r="D196" s="3" t="n">
-        <v>65.70999999999999</v>
+        <v>61.99</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>Огурцы Ботаника 420 г</t>
+          <t>Горчица Красная цена Столовая острая 150г</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -4381,18 +4381,18 @@
         </is>
       </c>
       <c r="D197" s="3" t="n">
-        <v>62.39</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>Печенье Мария Любятово</t>
+          <t>Рис круглозернистый шлифованный 900г</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -4401,18 +4401,18 @@
         </is>
       </c>
       <c r="D198" s="3" t="n">
-        <v>62.24</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>Попкорн Mixbar Party</t>
+          <t>Хлебцы Щедрые ржаные 100г</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -4421,18 +4421,18 @@
         </is>
       </c>
       <c r="D199" s="3" t="n">
-        <v>61.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>Горчица Красная цена Столовая острая 150г</t>
+          <t>Булочки Коломенский пшеничные</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -4441,13 +4441,13 @@
         </is>
       </c>
       <c r="D200" s="3" t="n">
-        <v>61.98</v>
+        <v>57.99</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>Рис круглозернистый шлифованный 900г</t>
+          <t>Макароны Makfa витки 450г</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4461,18 +4461,18 @@
         </is>
       </c>
       <c r="D201" s="3" t="n">
-        <v>60.8</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>Хлебцы Щедрые ржаные 100г</t>
+          <t>Макароны Makfa спирали экспресс 400г</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -4481,18 +4481,18 @@
         </is>
       </c>
       <c r="D202" s="3" t="n">
-        <v>59.99</v>
+        <v>57.76</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>Булочки Коломенский пшеничные</t>
+          <t>Огурцы среднеплодные 1кг</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -4501,18 +4501,18 @@
         </is>
       </c>
       <c r="D203" s="3" t="n">
-        <v>57.99</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>Макароны Makfa витки 450г</t>
+          <t>Яйцо С2</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Яйца</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -4521,18 +4521,18 @@
         </is>
       </c>
       <c r="D204" s="3" t="n">
-        <v>57.76</v>
+        <v>55</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>Макароны Makfa спирали экспресс 400г</t>
+          <t>Морковь отечественная</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -4541,18 +4541,18 @@
         </is>
       </c>
       <c r="D205" s="3" t="n">
-        <v>57.76</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>Огурцы среднеплодные 1кг</t>
+          <t>Снежок ФрутоНяня</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -4561,18 +4561,18 @@
         </is>
       </c>
       <c r="D206" s="3" t="n">
-        <v>56.65</v>
+        <v>53.99</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>Яйцо С2</t>
+          <t>Печенье детское Бегемотик Бонди кальций</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Яйца</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -4581,18 +4581,18 @@
         </is>
       </c>
       <c r="D207" s="3" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>Морковь отечественная</t>
+          <t>Печенье Юбилейное</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -4601,18 +4601,18 @@
         </is>
       </c>
       <c r="D208" s="3" t="n">
-        <v>54.28</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>Снежок ФрутоНяня</t>
+          <t>Яблоки фасованные ~1</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -4621,18 +4621,18 @@
         </is>
       </c>
       <c r="D209" s="3" t="n">
-        <v>53.99</v>
+        <v>52.72</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>Печенье детское Бегемотик Бонди кальций</t>
+          <t>Творог мягкий Искренне Ваш</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -4641,18 +4641,18 @@
         </is>
       </c>
       <c r="D210" s="3" t="n">
-        <v>53</v>
+        <v>50.99</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Печенье Юбилейное</t>
+          <t>Батон Хлебный Дом Звездный нарезка 350г</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -4661,18 +4661,18 @@
         </is>
       </c>
       <c r="D211" s="3" t="n">
-        <v>52.99</v>
+        <v>50.93</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Яблоки фасованные ~1</t>
+          <t>Творог Простоквашино Нежный мягкий</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -4681,18 +4681,18 @@
         </is>
       </c>
       <c r="D212" s="3" t="n">
-        <v>52.72</v>
+        <v>50.25</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Творог мягкий Искренне Ваш</t>
+          <t>Огурцы гладкие ~450 г</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -4701,18 +4701,18 @@
         </is>
       </c>
       <c r="D213" s="3" t="n">
-        <v>50.99</v>
+        <v>49.72</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>Батон Хлебный Дом Звездный нарезка 350г</t>
+          <t>Макаронные изделия Barilla Пенне Ригате №73 из</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -4721,18 +4721,18 @@
         </is>
       </c>
       <c r="D214" s="3" t="n">
-        <v>50.93</v>
+        <v>48.76</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>Творог Простоквашино Нежный мягкий</t>
+          <t>Пюре ФрутоНяня Салатик</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -4741,18 +4741,18 @@
         </is>
       </c>
       <c r="D215" s="3" t="n">
-        <v>50.25</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>Огурцы гладкие ~450 г</t>
+          <t>Пюре ФрутоНяня Яблоко, банан, груша с</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -4761,18 +4761,18 @@
         </is>
       </c>
       <c r="D216" s="3" t="n">
-        <v>49.72</v>
+        <v>46.99</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>Макаронные изделия Barilla Пенне Ригате №73 из</t>
+          <t>Капуста белокочанная</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -4781,18 +4781,18 @@
         </is>
       </c>
       <c r="D217" s="3" t="n">
-        <v>48.76</v>
+        <v>46.96</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>Пюре ФрутоНяня Салатик</t>
+          <t>Молоко сгущённое с сахаром Алексеевское</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Молочные продукты</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -4801,13 +4801,13 @@
         </is>
       </c>
       <c r="D218" s="3" t="n">
-        <v>46.99</v>
+        <v>45</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>Пюре ФрутоНяня Яблоко, банан, груша с</t>
+          <t>Апельсины</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -4821,18 +4821,18 @@
         </is>
       </c>
       <c r="D219" s="3" t="n">
-        <v>46.99</v>
+        <v>43.79</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>Капуста белокочанная</t>
+          <t>Печенье Любятово Мария традиционное</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -4841,18 +4841,18 @@
         </is>
       </c>
       <c r="D220" s="3" t="n">
-        <v>46.96</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>Молоко сгущённое с сахаром Алексеевское</t>
+          <t>Печенье Honey Kid Детское</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Молочные продукты</t>
+          <t>Сладости и снеки</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -4861,13 +4861,13 @@
         </is>
       </c>
       <c r="D221" s="3" t="n">
-        <v>45</v>
+        <v>38.24</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>Апельсины</t>
+          <t>Манго жёлтое</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -4881,18 +4881,18 @@
         </is>
       </c>
       <c r="D222" s="3" t="n">
-        <v>43.79</v>
+        <v>38</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>Печенье Любятово Мария традиционное</t>
+          <t>Батон Мосхлеб нарезной</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -4901,13 +4901,13 @@
         </is>
       </c>
       <c r="D223" s="3" t="n">
-        <v>42.99</v>
+        <v>38</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>Печенье Honey Kid Детское</t>
+          <t>Печенье Коломенское Овсяное злаковое</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -4921,18 +4921,18 @@
         </is>
       </c>
       <c r="D224" s="3" t="n">
-        <v>38.24</v>
+        <v>37.2</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>Манго жёлтое</t>
+          <t>Батон Селяночка Нарезной нарезка 400г</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -4941,18 +4941,18 @@
         </is>
       </c>
       <c r="D225" s="3" t="n">
-        <v>38</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>Батон Мосхлеб нарезной</t>
+          <t>Кисель ФрутоНяня клубника-малина</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -4961,18 +4961,18 @@
         </is>
       </c>
       <c r="D226" s="3" t="n">
-        <v>38</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>Печенье Коломенское Овсяное злаковое</t>
+          <t>Свекла ВкусВилл ~760 г</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Сладости и снеки</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -4981,18 +4981,18 @@
         </is>
       </c>
       <c r="D227" s="3" t="n">
-        <v>37.2</v>
+        <v>23.94</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>Батон Селяночка Нарезной нарезка 400г</t>
+          <t>Соль поваренная пищевая мелкая 1кг</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Бакалея и специи</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -5001,18 +5001,18 @@
         </is>
       </c>
       <c r="D228" s="3" t="n">
-        <v>31.5</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>Кисель ФрутоНяня клубника-малина</t>
+          <t>Гречка ядрица 900г</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Фрукты и ягоды</t>
+          <t>Крупы и макароны</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -5021,18 +5021,18 @@
         </is>
       </c>
       <c r="D229" s="3" t="n">
-        <v>31.5</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>Свекла ВкусВилл ~760 г</t>
+          <t>Хлеб Красная Цена Белый 380г</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Хлеб и выпечка</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -5041,18 +5041,18 @@
         </is>
       </c>
       <c r="D230" s="3" t="n">
-        <v>23.94</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>Соль поваренная пищевая мелкая 1кг</t>
+          <t>Свекла</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Бакалея и специи</t>
+          <t>Овощи и зелень</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -5061,18 +5061,18 @@
         </is>
       </c>
       <c r="D231" s="3" t="n">
-        <v>22.99</v>
+        <v>18.24</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>Гречка ядрица 900г</t>
+          <t>Пакет ПЯТЕРОЧКА 65х40см</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Крупы и макароны</t>
+          <t>Упаковка/прочее</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -5081,18 +5081,18 @@
         </is>
       </c>
       <c r="D232" s="3" t="n">
-        <v>20.16</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>Хлеб Красная Цена Белый 380г</t>
+          <t>Мешки для мусора</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Хлеб и выпечка</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -5101,18 +5101,18 @@
         </is>
       </c>
       <c r="D233" s="3" t="n">
-        <v>19.99</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>Свекла</t>
+          <t>Лаки Миши в ассортименте</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Овощи и зелень</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -5121,18 +5121,18 @@
         </is>
       </c>
       <c r="D234" s="3" t="n">
-        <v>18.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>Пакет ПЯТЕРОЧКА 65х40см</t>
+          <t>Доставка H99979765568</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Упаковка/прочее</t>
+          <t>Прочее</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -5141,13 +5141,13 @@
         </is>
       </c>
       <c r="D235" s="3" t="n">
-        <v>9.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>Мешки для мусора</t>
+          <t>Сборка</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5161,18 +5161,18 @@
         </is>
       </c>
       <c r="D236" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>Лаки Миши в ассортименте</t>
+          <t>Игрушка АМНЯМАНИЯ 2 в ассортименте</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Прочее</t>
+          <t>Фрукты и ягоды</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -5181,66 +5181,6 @@
         </is>
       </c>
       <c r="D237" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" s="2" t="inlineStr">
-        <is>
-          <t>Доставка H99979765568</t>
-        </is>
-      </c>
-      <c r="B238" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C238" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D238" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>Сборка</t>
-        </is>
-      </c>
-      <c r="B239" t="inlineStr">
-        <is>
-          <t>Прочее</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D239" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>Игрушка АМНЯМАНИЯ 2 в ассортименте</t>
-        </is>
-      </c>
-      <c r="B240" t="inlineStr">
-        <is>
-          <t>Фрукты и ягоды</t>
-        </is>
-      </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="D240" s="3" t="n">
         <v>0</v>
       </c>
     </row>
